--- a/AAII_Financials/Quarterly/GFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
   <si>
     <t>GFS</t>
   </si>
@@ -656,380 +656,392 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1786000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1634000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1830000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1688000</v>
       </c>
       <c r="G8" s="3">
         <v>1688000</v>
       </c>
       <c r="H8" s="3">
+        <v>1688000</v>
+      </c>
+      <c r="I8" s="3">
         <v>1585000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1830000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1739000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1632000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1549000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1854000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1852000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1845000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1841000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2101000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2074000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1993000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1940000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1846900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1700000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1620000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1418000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1062000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1091000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1318000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1379000</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1281000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1183000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1322000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1269000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1280000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1230000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1381000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1325000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1237000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1156000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1329000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1323000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1313000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1326000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1479000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1464000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1455000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1471000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1463600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1400000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1389000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>844000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1225000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1135000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1557000</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E10" s="3">
         <v>451000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>508000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>419000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>408000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>355000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>449000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>414000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>395000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>393000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>525000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>529000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>532000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>515000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>622000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>610000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>538000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>469000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>383300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>300000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>231000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>99000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>218000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-134000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>183000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-178000</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1060,83 +1072,84 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E12" s="3">
         <v>132000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>133000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>124000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>134000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>127000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>121000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>130000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>121000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>124000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>105000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>108000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>106000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>109000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>110000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>124000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>120000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>128000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>129500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>114000</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="3">
         <v>117000</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1146,8 +1159,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1232,56 +1248,59 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-7000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-31000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>936000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>43000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>17000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>19000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-309000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1297,8 +1316,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1318,53 +1337,56 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E15" s="3">
         <v>295000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>287000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>302000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>323000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>339000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>359000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>375000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>382000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>377000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>383000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>352000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>309000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>343000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1404,8 +1426,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1433,85 +1458,86 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1612000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1454000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1575000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1493000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1492000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1434000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1595000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1553000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1472000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1402000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1521000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1574000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1551000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1546000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1410000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1717000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1696000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1715000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1760800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1648000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="3">
         <v>1441000</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>0</v>
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC17" s="3">
         <v>0</v>
@@ -1519,94 +1545,100 @@
       <c r="AD17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E18" s="3">
         <v>180000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>255000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>195000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>196000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>151000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>235000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>186000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>160000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>147000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>333000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>278000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>294000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>295000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>691000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>357000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>297000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>225000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>86100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>52000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-350000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>1379000</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1637,169 +1669,173 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E20" s="3">
         <v>10000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>22000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-17000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>21000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>10000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-15000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-18100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-25000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1379000</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>432000</v>
+      </c>
+      <c r="E21" s="3">
         <v>465000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>520000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>498000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>536000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>489000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>588000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>556000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>538000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>522000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>708000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>609000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>593000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>624000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1085000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>750000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>705000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>615000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1271900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-342700</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>1547600</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,52 +1845,55 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>50000</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>106000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>101000</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1895,85 +1934,88 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E23" s="3">
         <v>185000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>274000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>221000</v>
       </c>
       <c r="G23" s="3">
         <v>221000</v>
       </c>
       <c r="H23" s="3">
+        <v>221000</v>
+      </c>
+      <c r="I23" s="3">
         <v>195000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-687000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>195000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>167000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>155000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>299000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>243000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>265000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>277000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>676000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>355000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>294000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>207000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>68100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>27000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-349000</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>0</v>
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC23" s="3">
         <v>0</v>
@@ -1981,94 +2023,100 @@
       <c r="AD23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E24" s="3">
         <v>81000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>74000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-28000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-16000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>42000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>21000</v>
       </c>
       <c r="M24" s="3">
         <v>21000</v>
       </c>
       <c r="N24" s="3">
+        <v>21000</v>
+      </c>
+      <c r="O24" s="3">
         <v>-6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>30000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>29000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>25800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>22000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>20000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>36000</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2153,85 +2201,88 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E26" s="3">
         <v>104000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>200000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>249000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>228000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>211000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-729000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>178000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>155000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>134000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>278000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>249000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>237000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>254000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>668000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>336000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>264000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>178000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>42300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-293000</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>0</v>
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC26" s="3">
         <v>0</v>
@@ -2239,85 +2290,88 @@
       <c r="AD26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E27" s="3">
         <v>103000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>199000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>248000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>228000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>210000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-730000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>177000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>155000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>133000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>277000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>249000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>240000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>254000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>669000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>337000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>264000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>178000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>44100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-293000</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>0</v>
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC27" s="3">
         <v>0</v>
@@ -2325,8 +2379,11 @@
       <c r="AD27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2411,8 +2468,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2497,8 +2557,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2583,8 +2646,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2669,171 +2735,177 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-22000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>17000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-21000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-10000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>18100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>25000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1379000</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E33" s="3">
         <v>103000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>199000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>248000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>228000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>210000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-730000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>177000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>155000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>133000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>277000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>249000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>240000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>254000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>669000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>337000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>264000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>178000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>44100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-293000</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>0</v>
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC33" s="3">
         <v>0</v>
@@ -2841,8 +2913,11 @@
       <c r="AD33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2927,85 +3002,88 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E35" s="3">
         <v>103000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>199000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>248000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>228000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>210000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-730000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>177000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>155000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>133000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>277000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>249000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>240000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>254000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>669000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>337000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>264000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>178000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>44100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-293000</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>0</v>
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC35" s="3">
         <v>0</v>
@@ -3013,99 +3091,105 @@
       <c r="AD35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3136,8 +3220,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3168,74 +3253,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1087000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1849000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1809000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2016000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1790000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1596000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2192000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2286000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2184000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2247000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2387000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1880000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1832000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2256000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2352000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2541000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2474000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3264000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2939200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1019000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>804700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3254,74 +3340,77 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1270000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1154000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1241000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1268000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1305000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1281000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1194000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1187000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1183000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1110000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1055000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1014000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>955000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>653000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>622000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>567000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>525000</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3">
         <v>23200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3">
         <v>22200</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,74 +3429,77 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1458000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1279000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1578000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1332000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1439000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1397000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1406000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1266000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1110000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1166000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1368000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1374000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1186000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1229000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1487000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1169000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1247000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1210000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1207700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1059000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1175900</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3426,74 +3518,77 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1622000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1686000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1577000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1645000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1726000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1813000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1624000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1802000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1786000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1667000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1487000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1509000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1504000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1423000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1339000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1342000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1262000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1185000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1121300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1078000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1005300</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3512,53 +3607,56 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E45" s="3">
         <v>68000</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>65000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>96000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>57000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>17000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>30000</v>
       </c>
       <c r="N45" s="3">
         <v>30000</v>
       </c>
       <c r="O45" s="3">
+        <v>30000</v>
+      </c>
+      <c r="P45" s="3">
         <v>46000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>67000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3598,74 +3696,77 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5468000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6036000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6205000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6326000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6356000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6105000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6416000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6598000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6280000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6214000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6327000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5807000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5523000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5628000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5800000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5619000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5508000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5659000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5291300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3156000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3008200</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3684,74 +3785,77 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1175000</v>
+      </c>
+      <c r="E47" s="3">
         <v>996000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1148000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>978000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>823000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>820000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>915000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>860000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>778000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>807000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>547000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>466000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>516000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>323000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>790000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>365000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>293800</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3">
         <v>206800</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3770,74 +3874,77 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7676000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7807000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7792000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7821000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8000000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8125000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8260000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9442000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9744000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10304000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10164000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10594000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10789000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10829000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10596000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10218000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9410000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9173000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8713000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8466000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8290500</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3856,74 +3963,77 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1861000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1366000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1368000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>940000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>722000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>739000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>660000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>552000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>461000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>481000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>391000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>381000</v>
       </c>
       <c r="O49" s="3">
         <v>381000</v>
       </c>
       <c r="P49" s="3">
+        <v>381000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>369000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>363000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3">
         <v>376700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3">
         <v>471100</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3942,8 +4052,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4028,8 +4141,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4114,74 +4230,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>496000</v>
+      </c>
+      <c r="E52" s="3">
         <v>483000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>379000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>386000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>632000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>440000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>360000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>456000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>453000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>430000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>374000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>345000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>361000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>395000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>292000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1006000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1276000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1070000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>352800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1025000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>420000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4200,8 +4319,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4286,74 +4408,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16888000</v>
+      </c>
+      <c r="E54" s="3">
         <v>16897000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17141000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16708000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16803000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16479000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16799000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18105000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17927000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18454000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18044000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17844000</v>
-      </c>
-      <c r="O54" s="3">
-        <v>17815000</v>
       </c>
       <c r="P54" s="3">
         <v>17815000</v>
       </c>
       <c r="Q54" s="3">
+        <v>17815000</v>
+      </c>
+      <c r="R54" s="3">
         <v>17841000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17208000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16194000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15902000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15027600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12647000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12396500</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4372,8 +4497,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4404,8 +4532,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4436,74 +4565,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>420000</v>
+      </c>
+      <c r="E57" s="3">
         <v>419000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>491000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>513000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>389000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>430000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>406000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2003000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2105000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2153000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>511000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2321000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2320000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2400000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>532000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3">
         <v>551100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3">
         <v>798800</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4522,74 +4652,77 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E58" s="3">
         <v>150000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>155000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>133000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>137000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>134000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>843000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>634000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>621000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>590000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>606000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>251000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>282000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>276000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>298000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>244000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>262000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>281000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>432200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>466000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>478600</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4608,74 +4741,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1221000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1270000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1029000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1407000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1273000</v>
       </c>
       <c r="I59" s="3">
         <v>1273000</v>
       </c>
       <c r="J59" s="3">
+        <v>1273000</v>
+      </c>
+      <c r="K59" s="3">
         <v>86000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>108000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>111000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1486000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>176000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>188000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>219000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2529000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3628000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3051000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3039000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2179500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1958000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>868800</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4694,74 +4830,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2209000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2329000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2368000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2087000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2414000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2428000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3044000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2723000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2834000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2854000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3099000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2748000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2790000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2895000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3359000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3872000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3313000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3320000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3162900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2424000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2146200</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4780,74 +4919,77 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1519000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1574000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1552000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1530000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1547000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1497000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1478000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2215000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2132000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2510000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2151000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2468000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2501000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2622000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2558000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1972000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1908000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1830000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2006400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2075000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2167300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4866,74 +5008,77 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>628000</v>
+      </c>
+      <c r="E62" s="3">
         <v>559000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>408000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>420000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>488000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>469000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>449000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1343000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1412000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1534000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>282000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1512000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1659000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1694000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1964000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2283000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2315000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2413000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1825200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1646000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1150600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4952,8 +5097,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5038,8 +5186,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5124,8 +5275,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5210,74 +5364,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5014000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5149000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5158000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4942000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5335000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5375000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5975000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6523000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6628000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7157000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6893000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7013000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7241000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7508000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7928000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8168000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7587000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7563000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7052100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6145000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5526100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5296,8 +5453,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5328,8 +5488,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5414,8 +5575,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5500,8 +5664,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5586,8 +5753,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5672,74 +5842,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12178000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12278000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-12381000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-12580000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12828000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13056000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13266000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-12536000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12713000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12868000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13001000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-13278000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-13527000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-13767000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14021000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-14689000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-15026000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
         <v>-15468800</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3">
         <v>-15518000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5758,8 +5931,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5844,8 +6020,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5930,8 +6109,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6016,74 +6198,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11818000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11693000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11928000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11712000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11415000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11054000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10776000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11533000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11252000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11251000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11104000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10787000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10529000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10260000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9913000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9040000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8607000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8339000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7975500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6502000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6870400</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6102,8 +6287,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6188,176 +6376,182 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E81" s="3">
         <v>103000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>199000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>248000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>228000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>210000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-730000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>177000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>155000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>133000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>277000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>249000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>240000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>254000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>669000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>337000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>264000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>178000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>44100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-293000</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>0</v>
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC81" s="3">
         <v>0</v>
@@ -6365,8 +6559,11 @@
       <c r="AD81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6397,65 +6594,66 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E83" s="3">
         <v>352000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>252000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>396000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>402000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>392000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>370000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>333000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>307000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>312000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>370000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>358000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>363000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>356000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>409000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>395000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>411000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>408000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6468,12 +6666,12 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1896600</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6483,8 +6681,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6569,8 +6770,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6655,8 +6859,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6741,8 +6948,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6827,8 +7037,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6913,83 +7126,86 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E89" s="3">
         <v>542000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>374000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>595000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>431000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>331000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>457000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>375000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>402000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>488000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>684000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>416000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>546000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>479000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>491000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>679000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>609000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>845000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1147900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1109000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA89" s="3">
         <v>806100</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6999,8 +7215,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7031,83 +7250,84 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-411000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-312000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-208000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-189000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-159000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-166000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-135000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-162000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-99000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-229000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-305000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-304000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-390000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-805000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-991000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-613000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-812000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-643000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-717400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-323500</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-309800</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7117,8 +7337,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7203,8 +7426,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7289,83 +7515,86 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1119000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-51000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-527000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-329000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-207000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-211000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-92000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-263000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-170000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-95000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-313000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-888000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-586000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1051000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-764000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1604000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-639000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-626000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-362000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-289100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7375,8 +7604,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7407,8 +7639,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7451,8 +7684,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7493,8 +7726,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7579,8 +7815,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7665,8 +7904,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7751,83 +7993,86 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-450000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-53000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-40000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-35000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-717000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-452000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-294000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-87000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-54000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-81000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>360000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>157000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>207000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>118000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1399700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-525000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-386200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7837,83 +8082,86 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1000</v>
       </c>
       <c r="H101" s="3">
         <v>-1000</v>
       </c>
       <c r="I101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J101" s="3">
         <v>5000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-1000</v>
       </c>
       <c r="K101" s="3">
         <v>-1000</v>
       </c>
       <c r="L101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>11000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>11000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8000</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA101" s="3">
         <v>500</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7923,83 +8171,86 @@
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-762000</v>
+      </c>
+      <c r="E102" s="3">
         <v>40000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-207000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>226000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>194000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-596000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-94000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>102000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-63000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-140000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>507000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-424000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-96000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-189000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>67000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-790000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>325000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1920500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>214000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3">
         <v>131400</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8007,6 +8258,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
